--- a/data-manipulation-scripts/sheets-cleanup/sheets/ EXCENTRICO FREIO 15_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ EXCENTRICO FREIO 15_02.xlsx
@@ -334,7 +334,9 @@
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="2">
+        <v>2.0</v>
+      </c>
       <c r="D2" s="2">
         <v>22.0</v>
       </c>
